--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -1808,10 +1808,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317662</v>
+        <v>130317651</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,31 +1819,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1851,10 +1846,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506909</v>
+        <v>506984</v>
       </c>
       <c r="R11" t="n">
-        <v>6957693</v>
+        <v>6957972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1889,17 +1884,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1938,10 +1929,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317651</v>
+        <v>130317662</v>
       </c>
       <c r="B12" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,26 +1940,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1976,10 +1972,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506984</v>
+        <v>506909</v>
       </c>
       <c r="R12" t="n">
-        <v>6957972</v>
+        <v>6957693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,13 +2010,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317706</v>
+        <v>130317715</v>
       </c>
       <c r="B17" t="n">
         <v>80285</v>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506967</v>
+        <v>506979</v>
       </c>
       <c r="R17" t="n">
-        <v>6957903</v>
+        <v>6957909</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På en björkhögstubbe.</t>
+          <t>På sälg och även på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2674,22 +2674,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317715</v>
+        <v>130317706</v>
       </c>
       <c r="B18" t="n">
         <v>80285</v>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506979</v>
+        <v>506967</v>
       </c>
       <c r="R18" t="n">
-        <v>6957909</v>
+        <v>6957903</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På sälg och även på gran.</t>
+          <t>På en björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2805,22 +2805,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -1301,7 +1301,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317698</v>
+        <v>130317710</v>
       </c>
       <c r="B7" t="n">
         <v>80285</v>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506953</v>
+        <v>506973</v>
       </c>
       <c r="R7" t="n">
-        <v>6958489</v>
+        <v>6958484</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317710</v>
+        <v>130317698</v>
       </c>
       <c r="B8" t="n">
         <v>80285</v>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506973</v>
+        <v>506953</v>
       </c>
       <c r="R8" t="n">
-        <v>6958484</v>
+        <v>6958489</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -1301,7 +1301,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317710</v>
+        <v>130317698</v>
       </c>
       <c r="B7" t="n">
         <v>80285</v>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506973</v>
+        <v>506953</v>
       </c>
       <c r="R7" t="n">
-        <v>6958484</v>
+        <v>6958489</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317698</v>
+        <v>130317710</v>
       </c>
       <c r="B8" t="n">
         <v>80285</v>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506953</v>
+        <v>506973</v>
       </c>
       <c r="R8" t="n">
-        <v>6958489</v>
+        <v>6958484</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317651</v>
+        <v>130317662</v>
       </c>
       <c r="B11" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,26 +1819,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1846,10 +1851,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506984</v>
+        <v>506909</v>
       </c>
       <c r="R11" t="n">
-        <v>6957972</v>
+        <v>6957693</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1884,13 +1889,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1929,10 +1938,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317662</v>
+        <v>130317651</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,31 +1949,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1972,10 +1976,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506909</v>
+        <v>506984</v>
       </c>
       <c r="R12" t="n">
-        <v>6957693</v>
+        <v>6957972</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2010,17 +2014,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317715</v>
+        <v>130317706</v>
       </c>
       <c r="B17" t="n">
         <v>80285</v>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506979</v>
+        <v>506967</v>
       </c>
       <c r="R17" t="n">
-        <v>6957909</v>
+        <v>6957903</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg och även på gran.</t>
+          <t>På en björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2674,22 +2674,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317706</v>
+        <v>130317715</v>
       </c>
       <c r="B18" t="n">
         <v>80285</v>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506967</v>
+        <v>506979</v>
       </c>
       <c r="R18" t="n">
-        <v>6957903</v>
+        <v>6957909</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På en björkhögstubbe.</t>
+          <t>På sälg och även på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2805,22 +2805,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130317716</v>
       </c>
       <c r="B2" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>130317712</v>
       </c>
       <c r="B3" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317671</v>
+        <v>130317718</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>78940</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,50 +957,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506956</v>
+        <v>506963</v>
       </c>
       <c r="R4" t="n">
-        <v>6958085</v>
+        <v>6958046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1041,6 +1028,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1064,10 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317718</v>
+        <v>130317671</v>
       </c>
       <c r="B5" t="n">
-        <v>78937</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,37 +1063,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506963</v>
+        <v>506956</v>
       </c>
       <c r="R5" t="n">
-        <v>6958046</v>
+        <v>6958085</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1147,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>130317703</v>
       </c>
       <c r="B6" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>130317698</v>
       </c>
       <c r="B7" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>130317710</v>
       </c>
       <c r="B8" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130317725</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>130317651</v>
       </c>
       <c r="B12" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2189,41 +2189,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317672</v>
+        <v>130317707</v>
       </c>
       <c r="B14" t="n">
-        <v>80314</v>
+        <v>80288</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2231,10 +2227,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506981</v>
+        <v>506960</v>
       </c>
       <c r="R14" t="n">
-        <v>6957910</v>
+        <v>6957874</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2267,6 +2263,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2319,37 +2320,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317707</v>
+        <v>130317672</v>
       </c>
       <c r="B15" t="n">
-        <v>80285</v>
+        <v>80317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2357,10 +2362,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506960</v>
+        <v>506981</v>
       </c>
       <c r="R15" t="n">
-        <v>6957874</v>
+        <v>6957910</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2393,11 +2398,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2453,7 +2453,7 @@
         <v>130317711</v>
       </c>
       <c r="B16" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>130317706</v>
       </c>
       <c r="B17" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>130317715</v>
       </c>
       <c r="B18" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>130317652</v>
       </c>
       <c r="B19" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130317716</v>
       </c>
       <c r="B2" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>130317712</v>
       </c>
       <c r="B3" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317718</v>
+        <v>130317671</v>
       </c>
       <c r="B4" t="n">
-        <v>78940</v>
+        <v>58011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,37 +957,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506963</v>
+        <v>506956</v>
       </c>
       <c r="R4" t="n">
-        <v>6958046</v>
+        <v>6958085</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +1041,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1052,10 +1064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317671</v>
+        <v>130317718</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>78966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,50 +1075,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506956</v>
+        <v>506963</v>
       </c>
       <c r="R5" t="n">
-        <v>6958085</v>
+        <v>6958046</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,6 +1146,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>130317703</v>
       </c>
       <c r="B6" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>130317698</v>
       </c>
       <c r="B7" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>130317710</v>
       </c>
       <c r="B8" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130317725</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>130317667</v>
       </c>
       <c r="B10" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317662</v>
+        <v>130317651</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>83187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,31 +1819,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1851,10 +1846,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506909</v>
+        <v>506984</v>
       </c>
       <c r="R11" t="n">
-        <v>6957693</v>
+        <v>6957972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1889,17 +1884,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1938,10 +1929,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317651</v>
+        <v>130317662</v>
       </c>
       <c r="B12" t="n">
-        <v>83161</v>
+        <v>57852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,26 +1940,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1976,10 +1972,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506984</v>
+        <v>506909</v>
       </c>
       <c r="R12" t="n">
-        <v>6957972</v>
+        <v>6957693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,13 +2010,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>130317663</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2189,37 +2189,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317707</v>
+        <v>130317672</v>
       </c>
       <c r="B14" t="n">
-        <v>80288</v>
+        <v>80343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2227,10 +2231,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506960</v>
+        <v>506981</v>
       </c>
       <c r="R14" t="n">
-        <v>6957874</v>
+        <v>6957910</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2263,11 +2267,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2320,41 +2319,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317672</v>
+        <v>130317707</v>
       </c>
       <c r="B15" t="n">
-        <v>80317</v>
+        <v>80314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2362,10 +2357,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506981</v>
+        <v>506960</v>
       </c>
       <c r="R15" t="n">
-        <v>6957910</v>
+        <v>6957874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2398,6 +2393,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2453,7 +2453,7 @@
         <v>130317711</v>
       </c>
       <c r="B16" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>130317706</v>
       </c>
       <c r="B17" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>130317715</v>
       </c>
       <c r="B18" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>130317652</v>
       </c>
       <c r="B19" t="n">
-        <v>83161</v>
+        <v>83187</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -1811,7 +1811,7 @@
         <v>130317651</v>
       </c>
       <c r="B11" t="n">
-        <v>83187</v>
+        <v>83188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>130317652</v>
       </c>
       <c r="B19" t="n">
-        <v>83187</v>
+        <v>83188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -1811,7 +1811,7 @@
         <v>130317651</v>
       </c>
       <c r="B11" t="n">
-        <v>83188</v>
+        <v>83189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2189,41 +2189,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317672</v>
+        <v>130317707</v>
       </c>
       <c r="B14" t="n">
-        <v>80343</v>
+        <v>80314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2231,10 +2227,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506981</v>
+        <v>506960</v>
       </c>
       <c r="R14" t="n">
-        <v>6957910</v>
+        <v>6957874</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2267,6 +2263,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2319,37 +2320,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317707</v>
+        <v>130317672</v>
       </c>
       <c r="B15" t="n">
-        <v>80314</v>
+        <v>80343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2357,10 +2362,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506960</v>
+        <v>506981</v>
       </c>
       <c r="R15" t="n">
-        <v>6957874</v>
+        <v>6957910</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2393,11 +2398,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2841,7 +2841,7 @@
         <v>130317652</v>
       </c>
       <c r="B19" t="n">
-        <v>83188</v>
+        <v>83189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130317716</v>
       </c>
       <c r="B2" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>130317712</v>
       </c>
       <c r="B3" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317671</v>
+        <v>130317718</v>
       </c>
       <c r="B4" t="n">
-        <v>58011</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,50 +957,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506956</v>
+        <v>506963</v>
       </c>
       <c r="R4" t="n">
-        <v>6958085</v>
+        <v>6958046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1041,6 +1028,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1064,10 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317718</v>
+        <v>130317671</v>
       </c>
       <c r="B5" t="n">
-        <v>78966</v>
+        <v>58013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,37 +1063,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506963</v>
+        <v>506956</v>
       </c>
       <c r="R5" t="n">
-        <v>6958046</v>
+        <v>6958085</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1147,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>130317703</v>
       </c>
       <c r="B6" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>130317698</v>
       </c>
       <c r="B7" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>130317710</v>
       </c>
       <c r="B8" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130317725</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>130317667</v>
       </c>
       <c r="B10" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>130317651</v>
       </c>
       <c r="B11" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>130317662</v>
       </c>
       <c r="B12" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>130317663</v>
       </c>
       <c r="B13" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2189,37 +2189,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317707</v>
+        <v>130317672</v>
       </c>
       <c r="B14" t="n">
-        <v>80314</v>
+        <v>80345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2227,10 +2231,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506960</v>
+        <v>506981</v>
       </c>
       <c r="R14" t="n">
-        <v>6957874</v>
+        <v>6957910</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2263,11 +2267,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2320,41 +2319,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317672</v>
+        <v>130317707</v>
       </c>
       <c r="B15" t="n">
-        <v>80343</v>
+        <v>80316</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2362,10 +2357,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506981</v>
+        <v>506960</v>
       </c>
       <c r="R15" t="n">
-        <v>6957910</v>
+        <v>6957874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2398,6 +2393,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2453,7 +2453,7 @@
         <v>130317711</v>
       </c>
       <c r="B16" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>130317706</v>
       </c>
       <c r="B17" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>130317715</v>
       </c>
       <c r="B18" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>130317652</v>
       </c>
       <c r="B19" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -2189,41 +2189,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317672</v>
+        <v>130317707</v>
       </c>
       <c r="B14" t="n">
-        <v>80345</v>
+        <v>80316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2231,10 +2227,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506981</v>
+        <v>506960</v>
       </c>
       <c r="R14" t="n">
-        <v>6957910</v>
+        <v>6957874</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2267,6 +2263,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2319,37 +2320,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317707</v>
+        <v>130317672</v>
       </c>
       <c r="B15" t="n">
-        <v>80316</v>
+        <v>80345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2357,10 +2362,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506960</v>
+        <v>506981</v>
       </c>
       <c r="R15" t="n">
-        <v>6957874</v>
+        <v>6957910</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2393,11 +2398,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -1808,10 +1808,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317651</v>
+        <v>130317662</v>
       </c>
       <c r="B11" t="n">
-        <v>83191</v>
+        <v>57854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,26 +1819,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1846,10 +1851,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506984</v>
+        <v>506909</v>
       </c>
       <c r="R11" t="n">
-        <v>6957972</v>
+        <v>6957693</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1884,13 +1889,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1929,10 +1938,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317662</v>
+        <v>130317651</v>
       </c>
       <c r="B12" t="n">
-        <v>57854</v>
+        <v>83191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,31 +1949,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1972,10 +1976,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506909</v>
+        <v>506984</v>
       </c>
       <c r="R12" t="n">
-        <v>6957693</v>
+        <v>6957972</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2010,17 +2014,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130317716</v>
       </c>
       <c r="B2" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>130317712</v>
       </c>
       <c r="B3" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>130317718</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>130317671</v>
       </c>
       <c r="B5" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>130317703</v>
       </c>
       <c r="B6" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>130317698</v>
       </c>
       <c r="B7" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>130317710</v>
       </c>
       <c r="B8" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130317725</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>130317667</v>
       </c>
       <c r="B10" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>130317662</v>
       </c>
       <c r="B11" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>130317651</v>
       </c>
       <c r="B12" t="n">
-        <v>83191</v>
+        <v>83199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>130317663</v>
       </c>
       <c r="B13" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2189,37 +2189,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317707</v>
+        <v>130317672</v>
       </c>
       <c r="B14" t="n">
-        <v>80316</v>
+        <v>80353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2227,10 +2231,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506960</v>
+        <v>506981</v>
       </c>
       <c r="R14" t="n">
-        <v>6957874</v>
+        <v>6957910</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2263,11 +2267,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2320,41 +2319,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317672</v>
+        <v>130317707</v>
       </c>
       <c r="B15" t="n">
-        <v>80345</v>
+        <v>80324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2362,10 +2357,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506981</v>
+        <v>506960</v>
       </c>
       <c r="R15" t="n">
-        <v>6957910</v>
+        <v>6957874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2398,6 +2393,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2453,7 +2453,7 @@
         <v>130317711</v>
       </c>
       <c r="B16" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>130317706</v>
       </c>
       <c r="B17" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>130317715</v>
       </c>
       <c r="B18" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>130317652</v>
       </c>
       <c r="B19" t="n">
-        <v>83191</v>
+        <v>83199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130317716</v>
       </c>
       <c r="B2" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>130317712</v>
       </c>
       <c r="B3" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>130317718</v>
       </c>
       <c r="B4" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>130317671</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>130317703</v>
       </c>
       <c r="B6" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>130317698</v>
       </c>
       <c r="B7" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>130317710</v>
       </c>
       <c r="B8" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130317725</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>130317667</v>
       </c>
       <c r="B10" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317662</v>
+        <v>130317651</v>
       </c>
       <c r="B11" t="n">
-        <v>57862</v>
+        <v>83200</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,31 +1819,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1851,10 +1846,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506909</v>
+        <v>506984</v>
       </c>
       <c r="R11" t="n">
-        <v>6957693</v>
+        <v>6957972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1889,17 +1884,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1938,10 +1929,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317651</v>
+        <v>130317662</v>
       </c>
       <c r="B12" t="n">
-        <v>83199</v>
+        <v>57863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,26 +1940,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1976,10 +1972,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506984</v>
+        <v>506909</v>
       </c>
       <c r="R12" t="n">
-        <v>6957972</v>
+        <v>6957693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,13 +2010,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>130317663</v>
       </c>
       <c r="B13" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>130317672</v>
       </c>
       <c r="B14" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>130317707</v>
       </c>
       <c r="B15" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>130317711</v>
       </c>
       <c r="B16" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>130317706</v>
       </c>
       <c r="B17" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>130317715</v>
       </c>
       <c r="B18" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>130317652</v>
       </c>
       <c r="B19" t="n">
-        <v>83199</v>
+        <v>83200</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130317716</v>
       </c>
       <c r="B2" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>130317712</v>
       </c>
       <c r="B3" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317718</v>
+        <v>130317671</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>58023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,37 +957,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506963</v>
+        <v>506956</v>
       </c>
       <c r="R4" t="n">
-        <v>6958046</v>
+        <v>6958085</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +1041,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1052,10 +1064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317671</v>
+        <v>130317718</v>
       </c>
       <c r="B5" t="n">
-        <v>58022</v>
+        <v>78978</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,50 +1075,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506956</v>
+        <v>506963</v>
       </c>
       <c r="R5" t="n">
-        <v>6958085</v>
+        <v>6958046</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,6 +1146,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>130317703</v>
       </c>
       <c r="B6" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>130317698</v>
       </c>
       <c r="B7" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>130317710</v>
       </c>
       <c r="B8" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130317725</v>
       </c>
       <c r="B9" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317651</v>
+        <v>130317662</v>
       </c>
       <c r="B11" t="n">
-        <v>83200</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,26 +1819,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1846,10 +1851,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506984</v>
+        <v>506909</v>
       </c>
       <c r="R11" t="n">
-        <v>6957972</v>
+        <v>6957693</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1884,13 +1889,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1929,10 +1938,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317662</v>
+        <v>130317651</v>
       </c>
       <c r="B12" t="n">
-        <v>57863</v>
+        <v>83201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,31 +1949,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1972,10 +1976,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506909</v>
+        <v>506984</v>
       </c>
       <c r="R12" t="n">
-        <v>6957693</v>
+        <v>6957972</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2010,17 +2014,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>130317663</v>
       </c>
       <c r="B13" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2189,41 +2189,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317672</v>
+        <v>130317707</v>
       </c>
       <c r="B14" t="n">
-        <v>80354</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2231,10 +2227,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506981</v>
+        <v>506960</v>
       </c>
       <c r="R14" t="n">
-        <v>6957910</v>
+        <v>6957874</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2267,6 +2263,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2319,37 +2320,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317707</v>
+        <v>130317672</v>
       </c>
       <c r="B15" t="n">
-        <v>80325</v>
+        <v>80355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2357,10 +2362,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506960</v>
+        <v>506981</v>
       </c>
       <c r="R15" t="n">
-        <v>6957874</v>
+        <v>6957910</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2393,11 +2398,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2453,7 +2453,7 @@
         <v>130317711</v>
       </c>
       <c r="B16" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317706</v>
+        <v>130317715</v>
       </c>
       <c r="B17" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506967</v>
+        <v>506979</v>
       </c>
       <c r="R17" t="n">
-        <v>6957903</v>
+        <v>6957909</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På en björkhögstubbe.</t>
+          <t>På sälg och även på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2674,22 +2674,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2707,10 +2707,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317715</v>
+        <v>130317706</v>
       </c>
       <c r="B18" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506979</v>
+        <v>506967</v>
       </c>
       <c r="R18" t="n">
-        <v>6957909</v>
+        <v>6957903</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På sälg och även på gran.</t>
+          <t>På en björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2805,22 +2805,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
         <v>130317652</v>
       </c>
       <c r="B19" t="n">
-        <v>83200</v>
+        <v>83201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -946,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317671</v>
+        <v>130317718</v>
       </c>
       <c r="B4" t="n">
-        <v>58023</v>
+        <v>78978</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,50 +957,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506956</v>
+        <v>506963</v>
       </c>
       <c r="R4" t="n">
-        <v>6958085</v>
+        <v>6958046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1041,6 +1028,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1064,10 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317718</v>
+        <v>130317671</v>
       </c>
       <c r="B5" t="n">
-        <v>78978</v>
+        <v>58023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,37 +1063,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506963</v>
+        <v>506956</v>
       </c>
       <c r="R5" t="n">
-        <v>6958046</v>
+        <v>6958085</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1147,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317662</v>
+        <v>130317651</v>
       </c>
       <c r="B11" t="n">
-        <v>57864</v>
+        <v>83201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,31 +1819,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1851,10 +1846,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506909</v>
+        <v>506984</v>
       </c>
       <c r="R11" t="n">
-        <v>6957693</v>
+        <v>6957972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1889,17 +1884,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1938,10 +1929,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317651</v>
+        <v>130317662</v>
       </c>
       <c r="B12" t="n">
-        <v>83201</v>
+        <v>57864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,26 +1940,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1976,10 +1972,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506984</v>
+        <v>506909</v>
       </c>
       <c r="R12" t="n">
-        <v>6957972</v>
+        <v>6957693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,13 +2010,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2189,37 +2189,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317707</v>
+        <v>130317672</v>
       </c>
       <c r="B14" t="n">
-        <v>80326</v>
+        <v>80355</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2227,10 +2231,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506960</v>
+        <v>506981</v>
       </c>
       <c r="R14" t="n">
-        <v>6957874</v>
+        <v>6957910</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2263,11 +2267,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2320,41 +2319,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317672</v>
+        <v>130317707</v>
       </c>
       <c r="B15" t="n">
-        <v>80355</v>
+        <v>80326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2362,10 +2357,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506981</v>
+        <v>506960</v>
       </c>
       <c r="R15" t="n">
-        <v>6957910</v>
+        <v>6957874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2398,6 +2393,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2576,7 +2576,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317715</v>
+        <v>130317706</v>
       </c>
       <c r="B17" t="n">
         <v>80326</v>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506979</v>
+        <v>506967</v>
       </c>
       <c r="R17" t="n">
-        <v>6957909</v>
+        <v>6957903</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg och även på gran.</t>
+          <t>På en björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2674,22 +2674,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317706</v>
+        <v>130317715</v>
       </c>
       <c r="B18" t="n">
         <v>80326</v>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506967</v>
+        <v>506979</v>
       </c>
       <c r="R18" t="n">
-        <v>6957903</v>
+        <v>6957909</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På en björkhögstubbe.</t>
+          <t>På sälg och även på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2805,22 +2805,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -2189,41 +2189,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317672</v>
+        <v>130317707</v>
       </c>
       <c r="B14" t="n">
-        <v>80355</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2231,10 +2227,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506981</v>
+        <v>506960</v>
       </c>
       <c r="R14" t="n">
-        <v>6957910</v>
+        <v>6957874</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2267,6 +2263,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2319,37 +2320,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317707</v>
+        <v>130317672</v>
       </c>
       <c r="B15" t="n">
-        <v>80326</v>
+        <v>80355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2357,10 +2362,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506960</v>
+        <v>506981</v>
       </c>
       <c r="R15" t="n">
-        <v>6957874</v>
+        <v>6957910</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2393,11 +2398,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130317716</v>
+        <v>130317728</v>
       </c>
       <c r="B2" t="n">
-        <v>80340</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506945</v>
+        <v>506918</v>
       </c>
       <c r="R2" t="n">
-        <v>6957861</v>
+        <v>6958323</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 aspar.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,27 +768,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Tre aspar.</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula # Tre aspar.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,41 +796,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130317712</v>
+        <v>130317723</v>
       </c>
       <c r="B3" t="n">
-        <v>80340</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -853,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506953</v>
+        <v>506907</v>
       </c>
       <c r="R3" t="n">
-        <v>6958498</v>
+        <v>6958328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,11 +872,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar av lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -913,22 +889,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -946,32 +917,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317718</v>
+        <v>130317725</v>
       </c>
       <c r="B4" t="n">
-        <v>78992</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506963</v>
+        <v>506911</v>
       </c>
       <c r="R4" t="n">
-        <v>6958046</v>
+        <v>6957802</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,6 +993,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1035,6 +1011,21 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1052,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317671</v>
+        <v>130317651</v>
       </c>
       <c r="B5" t="n">
-        <v>58037</v>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,50 +1054,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506956</v>
+        <v>506984</v>
       </c>
       <c r="R5" t="n">
-        <v>6958085</v>
+        <v>6957972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,12 +1125,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1170,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130317703</v>
+        <v>130317652</v>
       </c>
       <c r="B6" t="n">
-        <v>80340</v>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,21 +1175,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1208,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506992</v>
+        <v>506976</v>
       </c>
       <c r="R6" t="n">
-        <v>6957996</v>
+        <v>6957898</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,11 +1240,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1268,22 +1257,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1301,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317698</v>
+        <v>130317717</v>
       </c>
       <c r="B7" t="n">
-        <v>80340</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1312,21 +1296,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1339,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506953</v>
+        <v>506939</v>
       </c>
       <c r="R7" t="n">
-        <v>6958489</v>
+        <v>6958101</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,11 +1361,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1395,26 +1374,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1432,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317710</v>
+        <v>130317718</v>
       </c>
       <c r="B8" t="n">
-        <v>80340</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,21 +1402,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1470,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506973</v>
+        <v>506963</v>
       </c>
       <c r="R8" t="n">
-        <v>6958484</v>
+        <v>6958046</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1508,11 +1467,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1526,26 +1480,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1563,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130317725</v>
+        <v>130317684</v>
       </c>
       <c r="B9" t="n">
-        <v>79235</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,21 +1508,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1601,10 +1535,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506911</v>
+        <v>507008</v>
       </c>
       <c r="R9" t="n">
-        <v>6957802</v>
+        <v>6958401</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1641,7 +1575,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,17 +1595,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1689,57 +1628,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317667</v>
+        <v>130317685</v>
       </c>
       <c r="B10" t="n">
-        <v>57067</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506986</v>
+        <v>507014</v>
       </c>
       <c r="R10" t="n">
-        <v>6957970</v>
+        <v>6958455</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1776,7 +1706,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1 individ som blev skrämd och lyfte i flykt.</t>
+          <t>Lunglav på en död sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,12 +1715,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1808,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317651</v>
+        <v>130317695</v>
       </c>
       <c r="B11" t="n">
-        <v>83215</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,21 +1770,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1846,10 +1797,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506984</v>
+        <v>506917</v>
       </c>
       <c r="R11" t="n">
-        <v>6957972</v>
+        <v>6958514</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1884,6 +1835,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lunglav på flera sälgar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1901,17 +1857,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1929,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317662</v>
+        <v>130317698</v>
       </c>
       <c r="B12" t="n">
-        <v>57878</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,31 +1901,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1972,10 +1928,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506909</v>
+        <v>506953</v>
       </c>
       <c r="R12" t="n">
-        <v>6957693</v>
+        <v>6958489</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2012,7 +1968,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2021,6 +1977,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2031,17 +1988,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2059,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130317663</v>
+        <v>130317699</v>
       </c>
       <c r="B13" t="n">
-        <v>57878</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,29 +2032,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2102,10 +2063,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506917</v>
+        <v>506945</v>
       </c>
       <c r="R13" t="n">
-        <v>6957687</v>
+        <v>6958463</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2142,7 +2103,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, högt upp på en gran.</t>
+          <t>Rikligt med lunglavsbålar på sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2151,6 +2112,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2161,17 +2123,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2189,41 +2156,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317672</v>
+        <v>130317703</v>
       </c>
       <c r="B14" t="n">
-        <v>80369</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2231,10 +2194,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506981</v>
+        <v>506992</v>
       </c>
       <c r="R14" t="n">
-        <v>6957910</v>
+        <v>6957996</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2267,6 +2230,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2319,10 +2287,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317707</v>
+        <v>130317704</v>
       </c>
       <c r="B15" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,10 +2325,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506960</v>
+        <v>506968</v>
       </c>
       <c r="R15" t="n">
-        <v>6957874</v>
+        <v>6957954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2450,10 +2418,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130317711</v>
+        <v>130317705</v>
       </c>
       <c r="B16" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2488,10 +2456,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506964</v>
+        <v>506971</v>
       </c>
       <c r="R16" t="n">
-        <v>6958502</v>
+        <v>6957930</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2524,6 +2492,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,7 +2552,7 @@
         <v>130317706</v>
       </c>
       <c r="B17" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2707,10 +2680,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317715</v>
+        <v>130317707</v>
       </c>
       <c r="B18" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2745,10 +2718,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506979</v>
+        <v>506960</v>
       </c>
       <c r="R18" t="n">
-        <v>6957909</v>
+        <v>6957874</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2785,7 +2758,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På sälg och även på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2838,10 +2811,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317652</v>
+        <v>130317710</v>
       </c>
       <c r="B19" t="n">
-        <v>83215</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2849,21 +2822,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2876,10 +2849,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506976</v>
+        <v>506973</v>
       </c>
       <c r="R19" t="n">
-        <v>6957898</v>
+        <v>6958484</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2914,6 +2887,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2931,17 +2909,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2956,6 +2939,1415 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130317711</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Björnsjön Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>506964</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6958502</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130317712</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Björnsjön Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>506953</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6958498</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt med bålar av lunglav på sälg.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130317715</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Björnsjön Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>506979</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6957909</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På sälg och även på gran.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130317716</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Björnsjön Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>506945</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6957861</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 aspar.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Tre aspar.</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula # Tre aspar.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130317672</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Björnsjön Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>506981</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6957910</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130317662</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Björnsjön Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>506909</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6957693</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130317663</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Björnsjön Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>506917</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6957687</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, högt upp på en gran.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130317665</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Björnsjön Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>506918</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6957701</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, högt upp på granstam.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130317667</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Björnsjön Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>506986</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6957970</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 individ som blev skrämd och lyfte i flykt.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130317671</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Björnsjön Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>506956</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6958085</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130317719</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Björnsjön Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>506940</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6958101</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5096,32 +5096,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134841707</v>
+        <v>130317667</v>
       </c>
       <c r="B39" t="n">
-        <v>57975</v>
+        <v>57141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506991</v>
+        <v>506986</v>
       </c>
       <c r="R39" t="n">
-        <v>6957870</v>
+        <v>6957970</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5173,22 +5173,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1 individ som blev skrämd och lyfte i flykt.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5199,48 +5194,53 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317667</v>
+        <v>130317671</v>
       </c>
       <c r="B40" t="n">
-        <v>57141</v>
+        <v>58114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5250,7 +5250,11 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5262,10 +5266,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506986</v>
+        <v>506956</v>
       </c>
       <c r="R40" t="n">
-        <v>6957970</v>
+        <v>6958085</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5298,11 +5302,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>1 individ som blev skrämd och lyfte i flykt.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5334,61 +5333,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317671</v>
+        <v>134955665</v>
       </c>
       <c r="B41" t="n">
-        <v>58114</v>
+        <v>99112</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506956</v>
+        <v>507021</v>
       </c>
       <c r="R41" t="n">
-        <v>6958085</v>
+        <v>6957934</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5415,12 +5398,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5431,28 +5414,23 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134955665</v>
+        <v>134959108</v>
       </c>
       <c r="B42" t="n">
         <v>99112</v>
@@ -5483,14 +5461,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507021</v>
+        <v>507019</v>
       </c>
       <c r="R42" t="n">
-        <v>6957934</v>
+        <v>6958429</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5549,45 +5527,61 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134959108</v>
+        <v>130317719</v>
       </c>
       <c r="B43" t="n">
-        <v>99112</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507019</v>
+        <v>506940</v>
       </c>
       <c r="R43" t="n">
-        <v>6958429</v>
+        <v>6958101</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5614,12 +5608,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5628,28 +5627,34 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317719</v>
+        <v>134841765</v>
       </c>
       <c r="B44" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5676,34 +5681,30 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506940</v>
+        <v>506988</v>
       </c>
       <c r="R44" t="n">
-        <v>6958101</v>
+        <v>6957858</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5727,17 +5728,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5746,31 +5752,25 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134841765</v>
+        <v>134841768</v>
       </c>
       <c r="B45" t="n">
         <v>99195</v>
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506988</v>
+        <v>506984</v>
       </c>
       <c r="R45" t="n">
-        <v>6957858</v>
+        <v>6958031</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5889,7 +5889,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134841768</v>
+        <v>134841771</v>
       </c>
       <c r="B46" t="n">
         <v>99195</v>
@@ -5919,12 +5919,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506984</v>
+        <v>506917</v>
       </c>
       <c r="R46" t="n">
-        <v>6958031</v>
+        <v>6958119</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6008,7 +6008,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134841771</v>
+        <v>134958910</v>
       </c>
       <c r="B47" t="n">
         <v>99195</v>
@@ -6038,30 +6038,22 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506917</v>
+        <v>507007</v>
       </c>
       <c r="R47" t="n">
-        <v>6958119</v>
+        <v>6958439</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6085,22 +6077,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:17</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6115,19 +6097,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134958910</v>
+        <v>134959507</v>
       </c>
       <c r="B48" t="n">
         <v>99195</v>
@@ -6157,19 +6139,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507007</v>
+        <v>507019</v>
       </c>
       <c r="R48" t="n">
-        <v>6958439</v>
+        <v>6957937</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6228,7 +6210,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134959507</v>
+        <v>134968003</v>
       </c>
       <c r="B49" t="n">
         <v>99195</v>
@@ -6258,7 +6240,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6267,10 +6249,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507019</v>
+        <v>507023</v>
       </c>
       <c r="R49" t="n">
-        <v>6957937</v>
+        <v>6957933</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6329,7 +6311,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134968003</v>
+        <v>134970241</v>
       </c>
       <c r="B50" t="n">
         <v>99195</v>
@@ -6359,19 +6341,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507023</v>
+        <v>507017</v>
       </c>
       <c r="R50" t="n">
-        <v>6957933</v>
+        <v>6958430</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6430,52 +6412,60 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134970241</v>
+        <v>134841775</v>
       </c>
       <c r="B51" t="n">
-        <v>99195</v>
+        <v>99217</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507017</v>
+        <v>506995</v>
       </c>
       <c r="R51" t="n">
-        <v>6958430</v>
+        <v>6957877</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6499,12 +6489,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6519,19 +6519,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134841775</v>
+        <v>134841778</v>
       </c>
       <c r="B52" t="n">
         <v>99217</v>
@@ -6559,16 +6559,8 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6578,10 +6570,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506995</v>
+        <v>506919</v>
       </c>
       <c r="R52" t="n">
-        <v>6957877</v>
+        <v>6957838</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6613,7 +6605,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6623,7 +6615,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6650,52 +6642,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134841778</v>
+        <v>134958065</v>
       </c>
       <c r="B53" t="n">
-        <v>99217</v>
+        <v>78382</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>228579</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506919</v>
+        <v>507010</v>
       </c>
       <c r="R53" t="n">
-        <v>6957838</v>
+        <v>6957909</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6719,22 +6707,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:31</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:31</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6749,112 +6727,15 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>134958065</v>
-      </c>
-      <c r="B54" t="n">
-        <v>78382</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Korsgräsnäset, Jmt</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>507010</v>
-      </c>
-      <c r="R54" t="n">
-        <v>6957909</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Bodsjö</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Via Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5096,32 +5096,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317667</v>
+        <v>134841707</v>
       </c>
       <c r="B39" t="n">
-        <v>57141</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506986</v>
+        <v>506991</v>
       </c>
       <c r="R39" t="n">
-        <v>6957970</v>
+        <v>6957870</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5173,17 +5173,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>1 individ som blev skrämd och lyfte i flykt.</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5194,53 +5199,48 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317671</v>
+        <v>130317667</v>
       </c>
       <c r="B40" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5250,11 +5250,7 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5266,10 +5262,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506956</v>
+        <v>506986</v>
       </c>
       <c r="R40" t="n">
-        <v>6958085</v>
+        <v>6957970</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5302,6 +5298,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>1 individ som blev skrämd och lyfte i flykt.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5333,45 +5334,61 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134955665</v>
+        <v>130317671</v>
       </c>
       <c r="B41" t="n">
-        <v>99112</v>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507021</v>
+        <v>506956</v>
       </c>
       <c r="R41" t="n">
-        <v>6957934</v>
+        <v>6958085</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5398,12 +5415,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5414,23 +5431,28 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134959108</v>
+        <v>134955665</v>
       </c>
       <c r="B42" t="n">
         <v>99112</v>
@@ -5461,14 +5483,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507019</v>
+        <v>507021</v>
       </c>
       <c r="R42" t="n">
-        <v>6958429</v>
+        <v>6957934</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5527,61 +5549,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317719</v>
+        <v>134959108</v>
       </c>
       <c r="B43" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506940</v>
+        <v>507019</v>
       </c>
       <c r="R43" t="n">
-        <v>6958101</v>
+        <v>6958429</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5608,17 +5614,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5627,34 +5628,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134841765</v>
+        <v>130317719</v>
       </c>
       <c r="B44" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5681,30 +5676,34 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506988</v>
+        <v>506940</v>
       </c>
       <c r="R44" t="n">
-        <v>6957858</v>
+        <v>6958101</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5728,22 +5727,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:21</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5752,25 +5746,31 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134841768</v>
+        <v>134841765</v>
       </c>
       <c r="B45" t="n">
         <v>99195</v>
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506984</v>
+        <v>506988</v>
       </c>
       <c r="R45" t="n">
-        <v>6958031</v>
+        <v>6957858</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5889,7 +5889,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134841771</v>
+        <v>134841768</v>
       </c>
       <c r="B46" t="n">
         <v>99195</v>
@@ -5919,12 +5919,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506917</v>
+        <v>506984</v>
       </c>
       <c r="R46" t="n">
-        <v>6958119</v>
+        <v>6958031</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6008,7 +6008,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134958910</v>
+        <v>134841771</v>
       </c>
       <c r="B47" t="n">
         <v>99195</v>
@@ -6038,22 +6038,30 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507007</v>
+        <v>506917</v>
       </c>
       <c r="R47" t="n">
-        <v>6958439</v>
+        <v>6958119</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6077,12 +6085,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6097,19 +6115,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134959507</v>
+        <v>134958910</v>
       </c>
       <c r="B48" t="n">
         <v>99195</v>
@@ -6139,19 +6157,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507019</v>
+        <v>507007</v>
       </c>
       <c r="R48" t="n">
-        <v>6957937</v>
+        <v>6958439</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6210,7 +6228,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134968003</v>
+        <v>134959507</v>
       </c>
       <c r="B49" t="n">
         <v>99195</v>
@@ -6240,7 +6258,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6249,10 +6267,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507023</v>
+        <v>507019</v>
       </c>
       <c r="R49" t="n">
-        <v>6957933</v>
+        <v>6957937</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6311,7 +6329,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134970241</v>
+        <v>134968003</v>
       </c>
       <c r="B50" t="n">
         <v>99195</v>
@@ -6341,19 +6359,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507017</v>
+        <v>507023</v>
       </c>
       <c r="R50" t="n">
-        <v>6958430</v>
+        <v>6957933</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6412,60 +6430,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134841775</v>
+        <v>134970241</v>
       </c>
       <c r="B51" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506995</v>
+        <v>507017</v>
       </c>
       <c r="R51" t="n">
-        <v>6957877</v>
+        <v>6958430</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6489,22 +6499,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6519,19 +6519,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134841778</v>
+        <v>134841775</v>
       </c>
       <c r="B52" t="n">
         <v>99217</v>
@@ -6559,8 +6559,16 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6570,10 +6578,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506919</v>
+        <v>506995</v>
       </c>
       <c r="R52" t="n">
-        <v>6957838</v>
+        <v>6957877</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6605,7 +6613,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6615,7 +6623,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6642,48 +6650,52 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134958065</v>
+        <v>134841778</v>
       </c>
       <c r="B53" t="n">
-        <v>78382</v>
+        <v>99217</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507010</v>
+        <v>506919</v>
       </c>
       <c r="R53" t="n">
-        <v>6957909</v>
+        <v>6957838</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6707,12 +6719,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6727,15 +6749,112 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134958065</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Korsgräsnäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>507010</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6957909</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
           <t>Caspar Ström</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
+      <c r="AX54" t="inlineStr">
         <is>
           <t>Via Caspar Ström</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966519</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317728</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966316</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963294</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317723</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317725</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841726</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955664</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,6 +1704,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317651</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1780,6 +1830,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317652</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1877,6 +1932,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969429</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1983,6 +2043,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317717</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2089,6 +2154,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317718</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2220,6 +2290,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317684</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2351,6 +2426,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317685</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2482,6 +2562,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317695</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2613,6 +2698,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317698</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2748,6 +2838,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317699</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2879,6 +2974,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317703</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3010,6 +3110,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317704</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3141,6 +3246,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317705</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3272,6 +3382,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317706</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3403,6 +3518,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317707</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3534,6 +3654,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317710</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3660,6 +3785,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317711</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3795,6 +3925,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317712</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3926,6 +4061,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317715</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4062,6 +4202,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317716</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4172,6 +4317,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841740</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4282,6 +4432,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841741</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4379,6 +4534,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967360</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4476,6 +4636,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967784</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4573,6 +4738,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956128</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4703,6 +4873,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317672</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4833,6 +5008,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317662</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4963,6 +5143,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317663</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5093,6 +5278,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317665</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5212,6 +5402,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841707</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5331,6 +5526,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317667</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5449,6 +5649,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317671</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5546,6 +5751,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955665</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5643,6 +5853,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959108</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5767,6 +5982,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317719</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5886,6 +6106,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841765</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6005,6 +6230,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841768</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6124,6 +6354,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841771</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6225,6 +6460,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958910</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6326,6 +6566,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959507</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6427,6 +6672,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968003</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6528,6 +6778,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970241</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6647,6 +6902,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841775</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6758,6 +7018,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841778</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6855,8 +7120,68 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958065</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ54"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5286,32 +5286,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134841707</v>
+        <v>130317667</v>
       </c>
       <c r="B39" t="n">
-        <v>57975</v>
+        <v>57141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5321,25 +5321,25 @@
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506991</v>
+        <v>506986</v>
       </c>
       <c r="R39" t="n">
-        <v>6957870</v>
+        <v>6957970</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5363,22 +5363,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1 individ som blev skrämd och lyfte i flykt.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5389,53 +5384,58 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841707</t>
+          <t>https://artportalen.se/Sighting/130317667</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317667</v>
+        <v>130317671</v>
       </c>
       <c r="B40" t="n">
-        <v>57141</v>
+        <v>58114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5445,7 +5445,11 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5457,10 +5461,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506986</v>
+        <v>506956</v>
       </c>
       <c r="R40" t="n">
-        <v>6957970</v>
+        <v>6958085</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5495,11 +5499,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>1 individ som blev skrämd och lyfte i flykt.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5528,67 +5527,51 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317667</t>
+          <t>https://artportalen.se/Sighting/130317671</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317671</v>
+        <v>134955665</v>
       </c>
       <c r="B41" t="n">
-        <v>58114</v>
+        <v>99112</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506956</v>
+        <v>507021</v>
       </c>
       <c r="R41" t="n">
-        <v>6958085</v>
+        <v>6957934</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5615,12 +5598,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5631,33 +5614,28 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317671</t>
+          <t>https://artportalen.se/Sighting/134955665</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134955665</v>
+        <v>134959108</v>
       </c>
       <c r="B42" t="n">
         <v>99112</v>
@@ -5688,14 +5666,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507021</v>
+        <v>507019</v>
       </c>
       <c r="R42" t="n">
-        <v>6957934</v>
+        <v>6958429</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5753,51 +5731,67 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134955665</t>
+          <t>https://artportalen.se/Sighting/134959108</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134959108</v>
+        <v>130317719</v>
       </c>
       <c r="B43" t="n">
-        <v>99112</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507019</v>
+        <v>506940</v>
       </c>
       <c r="R43" t="n">
-        <v>6958429</v>
+        <v>6958101</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5824,12 +5818,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5838,33 +5837,39 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134959108</t>
+          <t>https://artportalen.se/Sighting/130317719</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317719</v>
+        <v>134841765</v>
       </c>
       <c r="B44" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5891,34 +5896,30 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506940</v>
+        <v>506988</v>
       </c>
       <c r="R44" t="n">
-        <v>6958101</v>
+        <v>6957858</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5942,17 +5943,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5961,36 +5967,30 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317719</t>
+          <t>https://artportalen.se/Sighting/134841765</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134841765</v>
+        <v>134841768</v>
       </c>
       <c r="B45" t="n">
         <v>99195</v>
@@ -6020,12 +6020,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506988</v>
+        <v>506984</v>
       </c>
       <c r="R45" t="n">
-        <v>6957858</v>
+        <v>6958031</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6108,13 +6108,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841765</t>
+          <t>https://artportalen.se/Sighting/134841768</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134841768</v>
+        <v>134841771</v>
       </c>
       <c r="B46" t="n">
         <v>99195</v>
@@ -6144,12 +6144,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506984</v>
+        <v>506917</v>
       </c>
       <c r="R46" t="n">
-        <v>6958031</v>
+        <v>6958119</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6232,13 +6232,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841768</t>
+          <t>https://artportalen.se/Sighting/134841771</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134841771</v>
+        <v>134958910</v>
       </c>
       <c r="B47" t="n">
         <v>99195</v>
@@ -6268,30 +6268,22 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506917</v>
+        <v>507007</v>
       </c>
       <c r="R47" t="n">
-        <v>6958119</v>
+        <v>6958439</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6315,22 +6307,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:17</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6345,24 +6327,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841771</t>
+          <t>https://artportalen.se/Sighting/134958910</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134958910</v>
+        <v>134959507</v>
       </c>
       <c r="B48" t="n">
         <v>99195</v>
@@ -6392,19 +6374,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507007</v>
+        <v>507019</v>
       </c>
       <c r="R48" t="n">
-        <v>6958439</v>
+        <v>6957937</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6462,13 +6444,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134958910</t>
+          <t>https://artportalen.se/Sighting/134959507</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134959507</v>
+        <v>134968003</v>
       </c>
       <c r="B49" t="n">
         <v>99195</v>
@@ -6498,7 +6480,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6507,10 +6489,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507019</v>
+        <v>507023</v>
       </c>
       <c r="R49" t="n">
-        <v>6957937</v>
+        <v>6957933</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6568,13 +6550,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134959507</t>
+          <t>https://artportalen.se/Sighting/134968003</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134968003</v>
+        <v>134970241</v>
       </c>
       <c r="B50" t="n">
         <v>99195</v>
@@ -6604,19 +6586,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507023</v>
+        <v>507017</v>
       </c>
       <c r="R50" t="n">
-        <v>6957933</v>
+        <v>6958430</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6674,58 +6656,66 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134968003</t>
+          <t>https://artportalen.se/Sighting/134970241</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134970241</v>
+        <v>134841775</v>
       </c>
       <c r="B51" t="n">
-        <v>99195</v>
+        <v>99217</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507017</v>
+        <v>506995</v>
       </c>
       <c r="R51" t="n">
-        <v>6958430</v>
+        <v>6957877</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6749,12 +6739,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6769,24 +6769,24 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134970241</t>
+          <t>https://artportalen.se/Sighting/134841775</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134841775</v>
+        <v>134841778</v>
       </c>
       <c r="B52" t="n">
         <v>99217</v>
@@ -6814,16 +6814,8 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6833,10 +6825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506995</v>
+        <v>506919</v>
       </c>
       <c r="R52" t="n">
-        <v>6957877</v>
+        <v>6957838</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6868,7 +6860,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6878,7 +6870,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6904,58 +6896,54 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841775</t>
+          <t>https://artportalen.se/Sighting/134841778</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134841778</v>
+        <v>134958065</v>
       </c>
       <c r="B53" t="n">
-        <v>99217</v>
+        <v>78382</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>228579</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506919</v>
+        <v>507010</v>
       </c>
       <c r="R53" t="n">
-        <v>6957838</v>
+        <v>6957909</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6979,22 +6967,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:31</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:31</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7009,118 +6987,16 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134841778</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>134958065</v>
-      </c>
-      <c r="B54" t="n">
-        <v>78382</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Korsgräsnäset, Jmt</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>507010</v>
-      </c>
-      <c r="R54" t="n">
-        <v>6957909</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Bodsjö</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Via Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134958065</t>
         </is>
@@ -7180,7 +7056,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58903-2024 artfynd.xlsx
+++ b/artfynd/A 58903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ53"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>134966519</v>
       </c>
       <c r="B2" t="n">
-        <v>83353</v>
+        <v>83393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>134966316</v>
       </c>
       <c r="B4" t="n">
-        <v>91745</v>
+        <v>91786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>134963294</v>
       </c>
       <c r="B5" t="n">
-        <v>92943</v>
+        <v>92985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>134955664</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>134969429</v>
       </c>
       <c r="B12" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>134967360</v>
       </c>
       <c r="B32" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>134967784</v>
       </c>
       <c r="B33" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>134956128</v>
       </c>
       <c r="B34" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5286,32 +5286,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317667</v>
+        <v>134841707</v>
       </c>
       <c r="B39" t="n">
-        <v>57141</v>
+        <v>57980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5321,25 +5321,25 @@
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506986</v>
+        <v>506991</v>
       </c>
       <c r="R39" t="n">
-        <v>6957970</v>
+        <v>6957870</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5363,17 +5363,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>1 individ som blev skrämd och lyfte i flykt.</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5384,58 +5389,53 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317667</t>
+          <t>https://artportalen.se/Sighting/134841707</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317671</v>
+        <v>130317667</v>
       </c>
       <c r="B40" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5445,11 +5445,7 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5461,10 +5457,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506956</v>
+        <v>506986</v>
       </c>
       <c r="R40" t="n">
-        <v>6958085</v>
+        <v>6957970</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5499,6 +5495,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>1 individ som blev skrämd och lyfte i flykt.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5527,51 +5528,67 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317671</t>
+          <t>https://artportalen.se/Sighting/130317667</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134955665</v>
+        <v>130317671</v>
       </c>
       <c r="B41" t="n">
-        <v>99112</v>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507021</v>
+        <v>506956</v>
       </c>
       <c r="R41" t="n">
-        <v>6957934</v>
+        <v>6958085</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5598,12 +5615,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5614,31 +5631,36 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134955665</t>
+          <t>https://artportalen.se/Sighting/130317671</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134959108</v>
+        <v>134955665</v>
       </c>
       <c r="B42" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5666,14 +5688,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507019</v>
+        <v>507021</v>
       </c>
       <c r="R42" t="n">
-        <v>6958429</v>
+        <v>6957934</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5731,67 +5753,51 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134959108</t>
+          <t>https://artportalen.se/Sighting/134955665</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317719</v>
+        <v>134959108</v>
       </c>
       <c r="B43" t="n">
-        <v>99118</v>
+        <v>99159</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506940</v>
+        <v>507019</v>
       </c>
       <c r="R43" t="n">
-        <v>6958101</v>
+        <v>6958429</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5818,17 +5824,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5837,39 +5838,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317719</t>
+          <t>https://artportalen.se/Sighting/134959108</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134841765</v>
+        <v>130317719</v>
       </c>
       <c r="B44" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5896,30 +5891,34 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506988</v>
+        <v>506940</v>
       </c>
       <c r="R44" t="n">
-        <v>6957858</v>
+        <v>6958101</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5943,22 +5942,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:21</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5967,30 +5961,36 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841765</t>
+          <t>https://artportalen.se/Sighting/130317719</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134841768</v>
+        <v>134841765</v>
       </c>
       <c r="B45" t="n">
         <v>99195</v>
@@ -6020,12 +6020,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506984</v>
+        <v>506988</v>
       </c>
       <c r="R45" t="n">
-        <v>6958031</v>
+        <v>6957858</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6108,13 +6108,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841768</t>
+          <t>https://artportalen.se/Sighting/134841765</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134841771</v>
+        <v>134841768</v>
       </c>
       <c r="B46" t="n">
         <v>99195</v>
@@ -6144,12 +6144,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506917</v>
+        <v>506984</v>
       </c>
       <c r="R46" t="n">
-        <v>6958119</v>
+        <v>6958031</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6232,13 +6232,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841771</t>
+          <t>https://artportalen.se/Sighting/134841768</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134958910</v>
+        <v>134841771</v>
       </c>
       <c r="B47" t="n">
         <v>99195</v>
@@ -6268,22 +6268,30 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507007</v>
+        <v>506917</v>
       </c>
       <c r="R47" t="n">
-        <v>6958439</v>
+        <v>6958119</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6307,12 +6315,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6327,27 +6345,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134958910</t>
+          <t>https://artportalen.se/Sighting/134841771</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134959507</v>
+        <v>134958910</v>
       </c>
       <c r="B48" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6374,19 +6392,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507019</v>
+        <v>507007</v>
       </c>
       <c r="R48" t="n">
-        <v>6957937</v>
+        <v>6958439</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6444,16 +6462,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134959507</t>
+          <t>https://artportalen.se/Sighting/134958910</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134968003</v>
+        <v>134959507</v>
       </c>
       <c r="B49" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6480,7 +6498,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6489,10 +6507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507023</v>
+        <v>507019</v>
       </c>
       <c r="R49" t="n">
-        <v>6957933</v>
+        <v>6957937</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6550,16 +6568,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134968003</t>
+          <t>https://artportalen.se/Sighting/134959507</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134970241</v>
+        <v>134968003</v>
       </c>
       <c r="B50" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6586,19 +6604,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507017</v>
+        <v>507023</v>
       </c>
       <c r="R50" t="n">
-        <v>6958430</v>
+        <v>6957933</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6656,66 +6674,58 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134970241</t>
+          <t>https://artportalen.se/Sighting/134968003</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134841775</v>
+        <v>134970241</v>
       </c>
       <c r="B51" t="n">
-        <v>99217</v>
+        <v>99242</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506995</v>
+        <v>507017</v>
       </c>
       <c r="R51" t="n">
-        <v>6957877</v>
+        <v>6958430</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6739,22 +6749,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6769,24 +6769,24 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841775</t>
+          <t>https://artportalen.se/Sighting/134970241</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134841778</v>
+        <v>134841775</v>
       </c>
       <c r="B52" t="n">
         <v>99217</v>
@@ -6814,8 +6814,16 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6825,10 +6833,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506919</v>
+        <v>506995</v>
       </c>
       <c r="R52" t="n">
-        <v>6957838</v>
+        <v>6957877</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6860,7 +6868,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6870,7 +6878,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6896,54 +6904,58 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841778</t>
+          <t>https://artportalen.se/Sighting/134841775</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134958065</v>
+        <v>134841778</v>
       </c>
       <c r="B53" t="n">
-        <v>78382</v>
+        <v>99217</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507010</v>
+        <v>506919</v>
       </c>
       <c r="R53" t="n">
-        <v>6957909</v>
+        <v>6957838</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6967,12 +6979,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6987,16 +7009,118 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841778</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134958065</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78420</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Korsgräsnäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>507010</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6957909</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134958065</t>
         </is>
@@ -7056,6 +7180,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
